--- a/data/13Week Material Requirement 2026-08-31.xlsx
+++ b/data/13Week Material Requirement 2026-08-31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_39E93A289BFB6896AEB55944AACB4415F58DFDFF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C379C570-C18B-49F4-A67D-D1EBBCF7EBF6}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_39E93A289BFB6896AEB55944AACB4415F58DFDFF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCE3CCB2-112C-4831-B803-B5F725286F0D}"/>
   <bookViews>
     <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3641,7 +3641,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AB457"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3737,7 +3736,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>30</v>
       </c>
@@ -3823,7 +3822,7 @@
         <v>26784</v>
       </c>
     </row>
-    <row r="3" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
@@ -3909,7 +3908,7 @@
         <v>25200</v>
       </c>
     </row>
-    <row r="4" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>35</v>
       </c>
@@ -3995,7 +3994,7 @@
         <v>17640</v>
       </c>
     </row>
-    <row r="5" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>37</v>
       </c>
@@ -4081,7 +4080,7 @@
         <v>12726</v>
       </c>
     </row>
-    <row r="6" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>39</v>
       </c>
@@ -4167,7 +4166,7 @@
         <v>11520</v>
       </c>
     </row>
-    <row r="7" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>41</v>
       </c>
@@ -4253,7 +4252,7 @@
         <v>11520</v>
       </c>
     </row>
-    <row r="8" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>43</v>
       </c>
@@ -4339,7 +4338,7 @@
         <v>7308</v>
       </c>
     </row>
-    <row r="9" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>45</v>
       </c>
@@ -4425,7 +4424,7 @@
         <v>10206</v>
       </c>
     </row>
-    <row r="10" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -4511,7 +4510,7 @@
         <v>9828</v>
       </c>
     </row>
-    <row r="11" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>49</v>
       </c>
@@ -4597,7 +4596,7 @@
         <v>9072</v>
       </c>
     </row>
-    <row r="12" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>51</v>
       </c>
@@ -4683,7 +4682,7 @@
         <v>5688</v>
       </c>
     </row>
-    <row r="13" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>53</v>
       </c>
@@ -4769,7 +4768,7 @@
         <v>7416</v>
       </c>
     </row>
-    <row r="14" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>55</v>
       </c>
@@ -4855,7 +4854,7 @@
         <v>8532</v>
       </c>
     </row>
-    <row r="15" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>57</v>
       </c>
@@ -4941,7 +4940,7 @@
         <v>5922</v>
       </c>
     </row>
-    <row r="16" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>59</v>
       </c>
@@ -5027,7 +5026,7 @@
         <v>5792</v>
       </c>
     </row>
-    <row r="17" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>61</v>
       </c>
@@ -5113,7 +5112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>63</v>
       </c>
@@ -5199,7 +5198,7 @@
         <v>5796</v>
       </c>
     </row>
-    <row r="19" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>65</v>
       </c>
@@ -5285,7 +5284,7 @@
         <v>6678</v>
       </c>
     </row>
-    <row r="20" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>67</v>
       </c>
@@ -5371,7 +5370,7 @@
         <v>3906</v>
       </c>
     </row>
-    <row r="21" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>69</v>
       </c>
@@ -5457,7 +5456,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="22" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>71</v>
       </c>
@@ -5543,7 +5542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>73</v>
       </c>
@@ -5629,7 +5628,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="24" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>75</v>
       </c>
@@ -5715,7 +5714,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="25" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>77</v>
       </c>
@@ -5801,7 +5800,7 @@
         <v>8436</v>
       </c>
     </row>
-    <row r="26" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>79</v>
       </c>
@@ -5887,7 +5886,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="27" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>81</v>
       </c>
@@ -5973,7 +5972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>83</v>
       </c>
@@ -6059,7 +6058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>85</v>
       </c>
@@ -6145,7 +6144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>87</v>
       </c>
@@ -6231,7 +6230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>89</v>
       </c>
@@ -6317,7 +6316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>91</v>
       </c>
@@ -6403,7 +6402,7 @@
         <v>3552</v>
       </c>
     </row>
-    <row r="33" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>93</v>
       </c>
@@ -6489,7 +6488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>95</v>
       </c>
@@ -6575,7 +6574,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="35" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>97</v>
       </c>
@@ -6661,7 +6660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>99</v>
       </c>
@@ -6747,7 +6746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>101</v>
       </c>
@@ -6833,7 +6832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>103</v>
       </c>
@@ -6919,7 +6918,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="39" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>105</v>
       </c>
@@ -7005,7 +7004,7 @@
         <v>3552</v>
       </c>
     </row>
-    <row r="40" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>107</v>
       </c>
@@ -7091,7 +7090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>109</v>
       </c>
@@ -7177,7 +7176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>111</v>
       </c>
@@ -7263,7 +7262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>113</v>
       </c>
@@ -7349,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>115</v>
       </c>
@@ -7435,7 +7434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>117</v>
       </c>
@@ -7521,7 +7520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>119</v>
       </c>
@@ -7607,7 +7606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>121</v>
       </c>
@@ -7693,7 +7692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>123</v>
       </c>
@@ -7779,7 +7778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>125</v>
       </c>
@@ -7865,7 +7864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>127</v>
       </c>
@@ -7951,7 +7950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>129</v>
       </c>
@@ -8037,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>131</v>
       </c>
@@ -8123,7 +8122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>133</v>
       </c>
@@ -8209,7 +8208,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="54" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>135</v>
       </c>
@@ -8295,7 +8294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>137</v>
       </c>
@@ -8381,7 +8380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>139</v>
       </c>
@@ -8434,7 +8433,7 @@
         <v>0</v>
       </c>
       <c r="R56" s="6">
-        <v>0</v>
+        <v>9916</v>
       </c>
       <c r="S56" s="6">
         <v>0</v>
@@ -8467,7 +8466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>141</v>
       </c>
@@ -8553,7 +8552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>143</v>
       </c>
@@ -8639,7 +8638,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="59" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>145</v>
       </c>
@@ -8725,7 +8724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>147</v>
       </c>
@@ -8811,7 +8810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>149</v>
       </c>
@@ -8897,7 +8896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>151</v>
       </c>
@@ -8983,7 +8982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>153</v>
       </c>
@@ -9069,7 +9068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>155</v>
       </c>
@@ -9155,7 +9154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>157</v>
       </c>
@@ -9241,7 +9240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>159</v>
       </c>
@@ -9327,7 +9326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>161</v>
       </c>
@@ -9413,7 +9412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>163</v>
       </c>
@@ -9499,7 +9498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>165</v>
       </c>
@@ -9585,7 +9584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>167</v>
       </c>
@@ -9671,7 +9670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>169</v>
       </c>
@@ -9757,7 +9756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>171</v>
       </c>
@@ -9843,7 +9842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>173</v>
       </c>
@@ -9929,7 +9928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>175</v>
       </c>
@@ -10015,7 +10014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>177</v>
       </c>
@@ -10101,7 +10100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>179</v>
       </c>
@@ -10187,7 +10186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>181</v>
       </c>
@@ -10273,7 +10272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>183</v>
       </c>
@@ -10359,7 +10358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>185</v>
       </c>
@@ -10445,7 +10444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>187</v>
       </c>
@@ -10531,7 +10530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>189</v>
       </c>
@@ -10617,7 +10616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>191</v>
       </c>
@@ -10703,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>193</v>
       </c>
@@ -10789,7 +10788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>195</v>
       </c>
@@ -10875,7 +10874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>197</v>
       </c>
@@ -10961,7 +10960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>199</v>
       </c>
@@ -11047,7 +11046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>201</v>
       </c>
@@ -11133,7 +11132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>203</v>
       </c>
@@ -11219,7 +11218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>205</v>
       </c>
@@ -11305,7 +11304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>207</v>
       </c>
@@ -11391,7 +11390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>209</v>
       </c>
@@ -11477,7 +11476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>211</v>
       </c>
@@ -11563,7 +11562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>213</v>
       </c>
@@ -11649,7 +11648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>215</v>
       </c>
@@ -11735,7 +11734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>217</v>
       </c>
@@ -11821,7 +11820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>219</v>
       </c>
@@ -11907,7 +11906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>221</v>
       </c>
@@ -11993,7 +11992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>223</v>
       </c>
@@ -12079,7 +12078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>225</v>
       </c>
@@ -12165,7 +12164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>227</v>
       </c>
@@ -12251,7 +12250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>229</v>
       </c>
@@ -12337,7 +12336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>231</v>
       </c>
@@ -12423,7 +12422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>233</v>
       </c>
@@ -12509,7 +12508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>235</v>
       </c>
@@ -12595,7 +12594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>237</v>
       </c>
@@ -12681,7 +12680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>239</v>
       </c>
@@ -12767,7 +12766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>241</v>
       </c>
@@ -12853,7 +12852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>243</v>
       </c>
@@ -12939,7 +12938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>245</v>
       </c>
@@ -13025,7 +13024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>247</v>
       </c>
@@ -13111,7 +13110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>249</v>
       </c>
@@ -13197,7 +13196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>251</v>
       </c>
@@ -13283,7 +13282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>253</v>
       </c>
@@ -13369,7 +13368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>255</v>
       </c>
@@ -13455,7 +13454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>257</v>
       </c>
@@ -13541,7 +13540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>259</v>
       </c>
@@ -13627,7 +13626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>261</v>
       </c>
@@ -13713,7 +13712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>263</v>
       </c>
@@ -13799,7 +13798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>265</v>
       </c>
@@ -13885,7 +13884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>267</v>
       </c>
@@ -13971,7 +13970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>269</v>
       </c>
@@ -14057,7 +14056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>271</v>
       </c>
@@ -14143,7 +14142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>273</v>
       </c>
@@ -14229,7 +14228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>275</v>
       </c>
@@ -14315,7 +14314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>277</v>
       </c>
@@ -14401,7 +14400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>279</v>
       </c>
@@ -14487,7 +14486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>281</v>
       </c>
@@ -14573,7 +14572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>283</v>
       </c>
@@ -14659,7 +14658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>285</v>
       </c>
@@ -14745,7 +14744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>287</v>
       </c>
@@ -14831,7 +14830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>289</v>
       </c>
@@ -14917,7 +14916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>291</v>
       </c>
@@ -15003,7 +15002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>293</v>
       </c>
@@ -15089,7 +15088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>295</v>
       </c>
@@ -15175,7 +15174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>297</v>
       </c>
@@ -15261,7 +15260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>299</v>
       </c>
@@ -15347,7 +15346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>301</v>
       </c>
@@ -15433,7 +15432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>303</v>
       </c>
@@ -15519,7 +15518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>305</v>
       </c>
@@ -15605,7 +15604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>307</v>
       </c>
@@ -15691,7 +15690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>309</v>
       </c>
@@ -15777,7 +15776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>311</v>
       </c>
@@ -15863,7 +15862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>313</v>
       </c>
@@ -15949,7 +15948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>315</v>
       </c>
@@ -16035,7 +16034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>317</v>
       </c>
@@ -16121,7 +16120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>319</v>
       </c>
@@ -16204,7 +16203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>320</v>
       </c>
@@ -16290,7 +16289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>322</v>
       </c>
@@ -16376,7 +16375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>324</v>
       </c>
@@ -16462,7 +16461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>326</v>
       </c>
@@ -16548,7 +16547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>328</v>
       </c>
@@ -16634,7 +16633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>330</v>
       </c>
@@ -16720,7 +16719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>332</v>
       </c>
@@ -16806,7 +16805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>334</v>
       </c>
@@ -16892,7 +16891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>336</v>
       </c>
@@ -16978,7 +16977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
         <v>338</v>
       </c>
@@ -17064,7 +17063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>340</v>
       </c>
@@ -17150,7 +17149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>342</v>
       </c>
@@ -17236,7 +17235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>344</v>
       </c>
@@ -17322,7 +17321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>346</v>
       </c>
@@ -17408,7 +17407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
         <v>348</v>
       </c>
@@ -17494,7 +17493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>350</v>
       </c>
@@ -17580,7 +17579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
         <v>352</v>
       </c>
@@ -17666,7 +17665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
         <v>354</v>
       </c>
@@ -17752,7 +17751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>356</v>
       </c>
@@ -17838,7 +17837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>358</v>
       </c>
@@ -17924,7 +17923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
         <v>360</v>
       </c>
@@ -18010,7 +18009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A168" s="5" t="s">
         <v>362</v>
       </c>
@@ -18096,7 +18095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
         <v>364</v>
       </c>
@@ -18182,7 +18181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
         <v>366</v>
       </c>
@@ -18268,7 +18267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
         <v>368</v>
       </c>
@@ -18354,7 +18353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A172" s="5" t="s">
         <v>370</v>
       </c>
@@ -18440,7 +18439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A173" s="5" t="s">
         <v>372</v>
       </c>
@@ -18526,7 +18525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
         <v>374</v>
       </c>
@@ -18612,7 +18611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
         <v>376</v>
       </c>
@@ -18698,7 +18697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A176" s="5" t="s">
         <v>378</v>
       </c>
@@ -18784,7 +18783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A177" s="5" t="s">
         <v>380</v>
       </c>
@@ -18870,7 +18869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A178" s="5" t="s">
         <v>382</v>
       </c>
@@ -18956,7 +18955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A179" s="5" t="s">
         <v>384</v>
       </c>
@@ -19042,7 +19041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>385</v>
       </c>
@@ -19128,7 +19127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>387</v>
       </c>
@@ -19214,7 +19213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>389</v>
       </c>
@@ -19300,7 +19299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>391</v>
       </c>
@@ -19386,7 +19385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>393</v>
       </c>
@@ -19472,7 +19471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>395</v>
       </c>
@@ -19558,7 +19557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A186" s="5" t="s">
         <v>397</v>
       </c>
@@ -19644,7 +19643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A187" s="5" t="s">
         <v>399</v>
       </c>
@@ -19730,7 +19729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
         <v>401</v>
       </c>
@@ -19816,7 +19815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
         <v>403</v>
       </c>
@@ -19902,7 +19901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A190" s="5" t="s">
         <v>405</v>
       </c>
@@ -19988,7 +19987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A191" s="5" t="s">
         <v>407</v>
       </c>
@@ -20074,7 +20073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A192" s="5" t="s">
         <v>409</v>
       </c>
@@ -20160,7 +20159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A193" s="5" t="s">
         <v>411</v>
       </c>
@@ -20246,7 +20245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
         <v>413</v>
       </c>
@@ -20332,7 +20331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A195" s="5" t="s">
         <v>415</v>
       </c>
@@ -20418,7 +20417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A196" s="5" t="s">
         <v>417</v>
       </c>
@@ -20504,7 +20503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A197" s="5" t="s">
         <v>419</v>
       </c>
@@ -20590,7 +20589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A198" s="5" t="s">
         <v>421</v>
       </c>
@@ -20676,7 +20675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A199" s="5" t="s">
         <v>423</v>
       </c>
@@ -20762,7 +20761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A200" s="5" t="s">
         <v>425</v>
       </c>
@@ -20848,7 +20847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A201" s="5" t="s">
         <v>427</v>
       </c>
@@ -20934,7 +20933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A202" s="5" t="s">
         <v>429</v>
       </c>
@@ -21020,7 +21019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A203" s="5" t="s">
         <v>431</v>
       </c>
@@ -21106,7 +21105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A204" s="5" t="s">
         <v>433</v>
       </c>
@@ -21192,7 +21191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
         <v>435</v>
       </c>
@@ -21278,7 +21277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A206" s="5" t="s">
         <v>437</v>
       </c>
@@ -21364,7 +21363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
         <v>439</v>
       </c>
@@ -21450,7 +21449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A208" s="5" t="s">
         <v>441</v>
       </c>
@@ -21536,7 +21535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A209" s="5" t="s">
         <v>443</v>
       </c>
@@ -21622,7 +21621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A210" s="5" t="s">
         <v>445</v>
       </c>
@@ -21708,7 +21707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
         <v>447</v>
       </c>
@@ -21794,7 +21793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
         <v>449</v>
       </c>
@@ -21880,7 +21879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
         <v>451</v>
       </c>
@@ -21966,7 +21965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
         <v>453</v>
       </c>
@@ -22052,7 +22051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
         <v>455</v>
       </c>
@@ -22138,7 +22137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A216" s="5" t="s">
         <v>457</v>
       </c>
@@ -22224,7 +22223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A217" s="5" t="s">
         <v>459</v>
       </c>
@@ -22310,7 +22309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A218" s="5" t="s">
         <v>461</v>
       </c>
@@ -22396,7 +22395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A219" s="5" t="s">
         <v>463</v>
       </c>
@@ -22482,7 +22481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A220" s="5" t="s">
         <v>465</v>
       </c>
@@ -22654,7 +22653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A222" s="5" t="s">
         <v>469</v>
       </c>
@@ -22740,7 +22739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A223" s="5" t="s">
         <v>471</v>
       </c>
@@ -22826,7 +22825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A224" s="5" t="s">
         <v>473</v>
       </c>
@@ -22912,7 +22911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A225" s="5" t="s">
         <v>475</v>
       </c>
@@ -22998,7 +22997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A226" s="5" t="s">
         <v>477</v>
       </c>
@@ -23084,7 +23083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A227" s="5" t="s">
         <v>479</v>
       </c>
@@ -23170,7 +23169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A228" s="5" t="s">
         <v>481</v>
       </c>
@@ -23256,7 +23255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>483</v>
       </c>
@@ -23342,7 +23341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>485</v>
       </c>
@@ -23428,7 +23427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
         <v>487</v>
       </c>
@@ -23514,7 +23513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
         <v>489</v>
       </c>
@@ -23600,7 +23599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A233" s="5" t="s">
         <v>491</v>
       </c>
@@ -23686,7 +23685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A234" s="5" t="s">
         <v>493</v>
       </c>
@@ -23772,7 +23771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A235" s="5" t="s">
         <v>495</v>
       </c>
@@ -23858,7 +23857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A236" s="5" t="s">
         <v>497</v>
       </c>
@@ -23944,7 +23943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A237" s="5" t="s">
         <v>499</v>
       </c>
@@ -24030,7 +24029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A238" s="5" t="s">
         <v>501</v>
       </c>
@@ -24116,7 +24115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A239" s="5" t="s">
         <v>503</v>
       </c>
@@ -24202,7 +24201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A240" s="5" t="s">
         <v>505</v>
       </c>
@@ -24288,7 +24287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A241" s="5" t="s">
         <v>507</v>
       </c>
@@ -24374,7 +24373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A242" s="5" t="s">
         <v>509</v>
       </c>
@@ -24460,7 +24459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A243" s="5" t="s">
         <v>511</v>
       </c>
@@ -24546,7 +24545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A244" s="5" t="s">
         <v>513</v>
       </c>
@@ -24632,7 +24631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A245" s="5" t="s">
         <v>515</v>
       </c>
@@ -24718,7 +24717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A246" s="5" t="s">
         <v>517</v>
       </c>
@@ -24804,7 +24803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A247" s="5" t="s">
         <v>519</v>
       </c>
@@ -24890,7 +24889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A248" s="5" t="s">
         <v>521</v>
       </c>
@@ -24976,7 +24975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A249" s="5" t="s">
         <v>523</v>
       </c>
@@ -25062,7 +25061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A250" s="5" t="s">
         <v>525</v>
       </c>
@@ -25148,7 +25147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A251" s="5" t="s">
         <v>527</v>
       </c>
@@ -25234,7 +25233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A252" s="5" t="s">
         <v>529</v>
       </c>
@@ -25320,7 +25319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A253" s="5" t="s">
         <v>531</v>
       </c>
@@ -25406,7 +25405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A254" s="5" t="s">
         <v>533</v>
       </c>
@@ -25492,7 +25491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A255" s="5" t="s">
         <v>535</v>
       </c>
@@ -25578,7 +25577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A256" s="5" t="s">
         <v>537</v>
       </c>
@@ -25664,7 +25663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A257" s="5" t="s">
         <v>539</v>
       </c>
@@ -25750,7 +25749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A258" s="5" t="s">
         <v>541</v>
       </c>
@@ -25836,7 +25835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A259" s="5" t="s">
         <v>543</v>
       </c>
@@ -25922,7 +25921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A260" s="5" t="s">
         <v>545</v>
       </c>
@@ -26008,7 +26007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A261" s="5" t="s">
         <v>547</v>
       </c>
@@ -26094,7 +26093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A262" s="5" t="s">
         <v>549</v>
       </c>
@@ -26180,7 +26179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A263" s="5" t="s">
         <v>551</v>
       </c>
@@ -26266,7 +26265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A264" s="5" t="s">
         <v>553</v>
       </c>
@@ -26352,7 +26351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A265" s="5" t="s">
         <v>555</v>
       </c>
@@ -26438,7 +26437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A266" s="5" t="s">
         <v>557</v>
       </c>
@@ -26524,7 +26523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A267" s="5" t="s">
         <v>559</v>
       </c>
@@ -26610,7 +26609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A268" s="5" t="s">
         <v>561</v>
       </c>
@@ -26696,7 +26695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A269" s="5" t="s">
         <v>563</v>
       </c>
@@ -26782,7 +26781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A270" s="5" t="s">
         <v>565</v>
       </c>
@@ -26868,7 +26867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A271" s="5" t="s">
         <v>567</v>
       </c>
@@ -26954,7 +26953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A272" s="5" t="s">
         <v>569</v>
       </c>
@@ -27040,7 +27039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A273" s="5" t="s">
         <v>571</v>
       </c>
@@ -27126,7 +27125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A274" s="5" t="s">
         <v>573</v>
       </c>
@@ -27212,7 +27211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A275" s="5" t="s">
         <v>575</v>
       </c>
@@ -27298,7 +27297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A276" s="5" t="s">
         <v>577</v>
       </c>
@@ -27384,7 +27383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A277" s="5" t="s">
         <v>579</v>
       </c>
@@ -27470,7 +27469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A278" s="5" t="s">
         <v>581</v>
       </c>
@@ -27556,7 +27555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A279" s="5" t="s">
         <v>583</v>
       </c>
@@ -27642,7 +27641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A280" s="5" t="s">
         <v>585</v>
       </c>
@@ -27728,7 +27727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A281" s="5" t="s">
         <v>587</v>
       </c>
@@ -27814,7 +27813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A282" s="5" t="s">
         <v>589</v>
       </c>
@@ -27900,7 +27899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A283" s="5" t="s">
         <v>591</v>
       </c>
@@ -27986,7 +27985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A284" s="5" t="s">
         <v>593</v>
       </c>
@@ -28072,7 +28071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A285" s="5" t="s">
         <v>595</v>
       </c>
@@ -28158,7 +28157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A286" s="5" t="s">
         <v>597</v>
       </c>
@@ -28244,7 +28243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A287" s="5" t="s">
         <v>599</v>
       </c>
@@ -28330,7 +28329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A288" s="5" t="s">
         <v>601</v>
       </c>
@@ -28416,7 +28415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A289" s="5" t="s">
         <v>603</v>
       </c>
@@ -28502,7 +28501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A290" s="5" t="s">
         <v>605</v>
       </c>
@@ -28588,7 +28587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A291" s="5" t="s">
         <v>607</v>
       </c>
@@ -28674,7 +28673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A292" s="5" t="s">
         <v>609</v>
       </c>
@@ -28760,7 +28759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A293" s="5" t="s">
         <v>611</v>
       </c>
@@ -28846,7 +28845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A294" s="5" t="s">
         <v>613</v>
       </c>
@@ -28932,7 +28931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A295" s="5" t="s">
         <v>615</v>
       </c>
@@ -29018,7 +29017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A296" s="5" t="s">
         <v>617</v>
       </c>
@@ -29104,7 +29103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A297" s="5" t="s">
         <v>619</v>
       </c>
@@ -29190,7 +29189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A298" s="5" t="s">
         <v>621</v>
       </c>
@@ -29276,7 +29275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A299" s="5" t="s">
         <v>623</v>
       </c>
@@ -29362,7 +29361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A300" s="5" t="s">
         <v>625</v>
       </c>
@@ -29448,7 +29447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A301" s="5" t="s">
         <v>627</v>
       </c>
@@ -29534,7 +29533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A302" s="5" t="s">
         <v>629</v>
       </c>
@@ -29620,7 +29619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A303" s="5" t="s">
         <v>631</v>
       </c>
@@ -29706,7 +29705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A304" s="5" t="s">
         <v>633</v>
       </c>
@@ -29792,7 +29791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A305" s="5" t="s">
         <v>635</v>
       </c>
@@ -29878,7 +29877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A306" s="5" t="s">
         <v>637</v>
       </c>
@@ -29964,7 +29963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A307" s="5" t="s">
         <v>639</v>
       </c>
@@ -30050,7 +30049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A308" s="5" t="s">
         <v>641</v>
       </c>
@@ -30136,7 +30135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A309" s="5" t="s">
         <v>643</v>
       </c>
@@ -30222,7 +30221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A310" s="5" t="s">
         <v>645</v>
       </c>
@@ -30308,7 +30307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A311" s="5" t="s">
         <v>647</v>
       </c>
@@ -30394,7 +30393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A312" s="5" t="s">
         <v>649</v>
       </c>
@@ -30480,7 +30479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A313" s="5" t="s">
         <v>651</v>
       </c>
@@ -30566,7 +30565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A314" s="5" t="s">
         <v>653</v>
       </c>
@@ -30652,7 +30651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A315" s="5" t="s">
         <v>655</v>
       </c>
@@ -30738,7 +30737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A316" s="5" t="s">
         <v>657</v>
       </c>
@@ -30824,7 +30823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A317" s="5" t="s">
         <v>659</v>
       </c>
@@ -30910,7 +30909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A318" s="5" t="s">
         <v>661</v>
       </c>
@@ -30996,7 +30995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A319" s="5" t="s">
         <v>663</v>
       </c>
@@ -31082,7 +31081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A320" s="5" t="s">
         <v>665</v>
       </c>
@@ -31168,7 +31167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A321" s="5" t="s">
         <v>667</v>
       </c>
@@ -31254,7 +31253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A322" s="5" t="s">
         <v>669</v>
       </c>
@@ -31340,7 +31339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A323" s="5" t="s">
         <v>671</v>
       </c>
@@ -31426,7 +31425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A324" s="5" t="s">
         <v>673</v>
       </c>
@@ -31512,7 +31511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A325" s="5" t="s">
         <v>675</v>
       </c>
@@ -31598,7 +31597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A326" s="5" t="s">
         <v>677</v>
       </c>
@@ -31684,7 +31683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A327" s="5" t="s">
         <v>679</v>
       </c>
@@ -31770,7 +31769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A328" s="5" t="s">
         <v>681</v>
       </c>
@@ -31856,7 +31855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A329" s="5" t="s">
         <v>683</v>
       </c>
@@ -31942,7 +31941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A330" s="5" t="s">
         <v>685</v>
       </c>
@@ -32028,7 +32027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A331" s="5" t="s">
         <v>687</v>
       </c>
@@ -32114,7 +32113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A332" s="5" t="s">
         <v>689</v>
       </c>
@@ -32200,7 +32199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A333" s="5" t="s">
         <v>691</v>
       </c>
@@ -32286,7 +32285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A334" s="5" t="s">
         <v>693</v>
       </c>
@@ -32372,7 +32371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A335" s="5" t="s">
         <v>695</v>
       </c>
@@ -32458,7 +32457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A336" s="5" t="s">
         <v>697</v>
       </c>
@@ -32544,7 +32543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A337" s="5" t="s">
         <v>699</v>
       </c>
@@ -32630,7 +32629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A338" s="5" t="s">
         <v>701</v>
       </c>
@@ -32716,7 +32715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A339" s="5" t="s">
         <v>703</v>
       </c>
@@ -32802,7 +32801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A340" s="5" t="s">
         <v>705</v>
       </c>
@@ -32888,7 +32887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A341" s="5" t="s">
         <v>707</v>
       </c>
@@ -32974,7 +32973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A342" s="5" t="s">
         <v>709</v>
       </c>
@@ -33060,7 +33059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A343" s="5" t="s">
         <v>711</v>
       </c>
@@ -33146,7 +33145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A344" s="5" t="s">
         <v>713</v>
       </c>
@@ -33232,7 +33231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A345" s="5" t="s">
         <v>715</v>
       </c>
@@ -33318,7 +33317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A346" s="5" t="s">
         <v>717</v>
       </c>
@@ -33404,7 +33403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A347" s="5" t="s">
         <v>719</v>
       </c>
@@ -33490,7 +33489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A348" s="5" t="s">
         <v>721</v>
       </c>
@@ -33576,7 +33575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A349" s="5" t="s">
         <v>723</v>
       </c>
@@ -33662,7 +33661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A350" s="5" t="s">
         <v>725</v>
       </c>
@@ -33748,7 +33747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A351" s="5" t="s">
         <v>727</v>
       </c>
@@ -33834,7 +33833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A352" s="5" t="s">
         <v>729</v>
       </c>
@@ -33920,7 +33919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A353" s="5" t="s">
         <v>731</v>
       </c>
@@ -34006,7 +34005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A354" s="5" t="s">
         <v>733</v>
       </c>
@@ -34092,7 +34091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A355" s="5" t="s">
         <v>735</v>
       </c>
@@ -34178,7 +34177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A356" s="5" t="s">
         <v>737</v>
       </c>
@@ -34264,7 +34263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A357" s="5" t="s">
         <v>739</v>
       </c>
@@ -34350,7 +34349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A358" s="5" t="s">
         <v>741</v>
       </c>
@@ -34436,7 +34435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A359" s="5" t="s">
         <v>743</v>
       </c>
@@ -34522,7 +34521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A360" s="5" t="s">
         <v>745</v>
       </c>
@@ -34608,7 +34607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A361" s="5" t="s">
         <v>747</v>
       </c>
@@ -34694,7 +34693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A362" s="5" t="s">
         <v>748</v>
       </c>
@@ -34780,7 +34779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A363" s="5" t="s">
         <v>750</v>
       </c>
@@ -34866,7 +34865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A364" s="5" t="s">
         <v>752</v>
       </c>
@@ -34952,7 +34951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A365" s="5" t="s">
         <v>754</v>
       </c>
@@ -35038,7 +35037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A366" s="5" t="s">
         <v>756</v>
       </c>
@@ -35124,7 +35123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A367" s="5" t="s">
         <v>758</v>
       </c>
@@ -35210,7 +35209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A368" s="5" t="s">
         <v>760</v>
       </c>
@@ -35296,7 +35295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A369" s="5" t="s">
         <v>762</v>
       </c>
@@ -35382,7 +35381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A370" s="5" t="s">
         <v>764</v>
       </c>
@@ -35468,7 +35467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A371" s="5" t="s">
         <v>766</v>
       </c>
@@ -35554,7 +35553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A372" s="5" t="s">
         <v>768</v>
       </c>
@@ -35640,7 +35639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A373" s="5" t="s">
         <v>770</v>
       </c>
@@ -35726,7 +35725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A374" s="5" t="s">
         <v>772</v>
       </c>
@@ -35812,7 +35811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A375" s="5" t="s">
         <v>774</v>
       </c>
@@ -35898,7 +35897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A376" s="5" t="s">
         <v>776</v>
       </c>
@@ -35984,7 +35983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A377" s="5" t="s">
         <v>778</v>
       </c>
@@ -36070,7 +36069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A378" s="5" t="s">
         <v>780</v>
       </c>
@@ -36156,7 +36155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A379" s="5" t="s">
         <v>782</v>
       </c>
@@ -36242,7 +36241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A380" s="5" t="s">
         <v>784</v>
       </c>
@@ -36328,7 +36327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A381" s="5" t="s">
         <v>786</v>
       </c>
@@ -36414,7 +36413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A382" s="5" t="s">
         <v>788</v>
       </c>
@@ -36500,7 +36499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A383" s="5" t="s">
         <v>790</v>
       </c>
@@ -36586,7 +36585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A384" s="5" t="s">
         <v>792</v>
       </c>
@@ -36672,7 +36671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A385" s="5" t="s">
         <v>794</v>
       </c>
@@ -36758,7 +36757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A386" s="5" t="s">
         <v>796</v>
       </c>
@@ -36844,7 +36843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A387" s="5" t="s">
         <v>798</v>
       </c>
@@ -36930,7 +36929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A388" s="5" t="s">
         <v>800</v>
       </c>
@@ -37016,7 +37015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A389" s="5" t="s">
         <v>802</v>
       </c>
@@ -37102,7 +37101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A390" s="5" t="s">
         <v>804</v>
       </c>
@@ -37188,7 +37187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A391" s="5" t="s">
         <v>806</v>
       </c>
@@ -37274,7 +37273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A392" s="5" t="s">
         <v>808</v>
       </c>
@@ -37360,7 +37359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A393" s="5" t="s">
         <v>810</v>
       </c>
@@ -37446,7 +37445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A394" s="5" t="s">
         <v>812</v>
       </c>
@@ -37532,7 +37531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A395" s="5" t="s">
         <v>814</v>
       </c>
@@ -37618,7 +37617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A396" s="5" t="s">
         <v>816</v>
       </c>
@@ -37704,7 +37703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A397" s="5" t="s">
         <v>818</v>
       </c>
@@ -37790,7 +37789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A398" s="5" t="s">
         <v>820</v>
       </c>
@@ -37876,7 +37875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A399" s="5" t="s">
         <v>822</v>
       </c>
@@ -37962,7 +37961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A400" s="5" t="s">
         <v>824</v>
       </c>
@@ -38048,7 +38047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A401" s="5" t="s">
         <v>826</v>
       </c>
@@ -38134,7 +38133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A402" s="5" t="s">
         <v>828</v>
       </c>
@@ -38220,7 +38219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A403" s="5" t="s">
         <v>830</v>
       </c>
@@ -38306,7 +38305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A404" s="5" t="s">
         <v>832</v>
       </c>
@@ -38392,7 +38391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A405" s="5" t="s">
         <v>834</v>
       </c>
@@ -38478,7 +38477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A406" s="5" t="s">
         <v>836</v>
       </c>
@@ -38564,7 +38563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A407" s="5" t="s">
         <v>838</v>
       </c>
@@ -38650,7 +38649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A408" s="5" t="s">
         <v>840</v>
       </c>
@@ -38736,7 +38735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A409" s="5" t="s">
         <v>842</v>
       </c>
@@ -38822,7 +38821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A410" s="5" t="s">
         <v>844</v>
       </c>
@@ -38908,7 +38907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A411" s="5" t="s">
         <v>846</v>
       </c>
@@ -38994,7 +38993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A412" s="5" t="s">
         <v>848</v>
       </c>
@@ -39080,7 +39079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A413" s="5" t="s">
         <v>850</v>
       </c>
@@ -39166,7 +39165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A414" s="5" t="s">
         <v>852</v>
       </c>
@@ -39252,7 +39251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A415" s="5" t="s">
         <v>854</v>
       </c>
@@ -39338,7 +39337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A416" s="5" t="s">
         <v>856</v>
       </c>
@@ -39424,7 +39423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A417" s="5" t="s">
         <v>858</v>
       </c>
@@ -39510,7 +39509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A418" s="5" t="s">
         <v>860</v>
       </c>
@@ -39596,7 +39595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A419" s="5" t="s">
         <v>862</v>
       </c>
@@ -39682,7 +39681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A420" s="5" t="s">
         <v>864</v>
       </c>
@@ -39768,7 +39767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A421" s="5" t="s">
         <v>866</v>
       </c>
@@ -39854,7 +39853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A422" s="5" t="s">
         <v>868</v>
       </c>
@@ -39940,7 +39939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A423" s="5" t="s">
         <v>870</v>
       </c>
@@ -40026,7 +40025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A424" s="5" t="s">
         <v>872</v>
       </c>
@@ -40112,7 +40111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A425" s="5" t="s">
         <v>874</v>
       </c>
@@ -40198,7 +40197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A426" s="5" t="s">
         <v>875</v>
       </c>
@@ -40284,7 +40283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A427" s="5" t="s">
         <v>877</v>
       </c>
@@ -40370,7 +40369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A428" s="5" t="s">
         <v>879</v>
       </c>
@@ -40456,7 +40455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A429" s="5" t="s">
         <v>881</v>
       </c>
@@ -40542,7 +40541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A430" s="5" t="s">
         <v>883</v>
       </c>
@@ -40628,7 +40627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A431" s="5" t="s">
         <v>885</v>
       </c>
@@ -40714,7 +40713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A432" s="5" t="s">
         <v>887</v>
       </c>
@@ -40800,7 +40799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A433" s="5" t="s">
         <v>889</v>
       </c>
@@ -40886,7 +40885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A434" s="5" t="s">
         <v>891</v>
       </c>
@@ -40972,7 +40971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A435" s="5" t="s">
         <v>893</v>
       </c>
@@ -41055,7 +41054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A436" s="5" t="s">
         <v>894</v>
       </c>
@@ -41141,7 +41140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A437" s="5" t="s">
         <v>896</v>
       </c>
@@ -41227,7 +41226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A438" s="5" t="s">
         <v>898</v>
       </c>
@@ -41313,7 +41312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A439" s="5" t="s">
         <v>900</v>
       </c>
@@ -41399,7 +41398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A440" s="5" t="s">
         <v>902</v>
       </c>
@@ -41485,7 +41484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A441" s="5" t="s">
         <v>904</v>
       </c>
@@ -41571,7 +41570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A442" s="5" t="s">
         <v>906</v>
       </c>
@@ -41657,7 +41656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A443" s="5" t="s">
         <v>908</v>
       </c>
@@ -41743,7 +41742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A444" s="5" t="s">
         <v>910</v>
       </c>
@@ -41829,7 +41828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A445" s="5" t="s">
         <v>912</v>
       </c>
@@ -41915,7 +41914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A446" s="5" t="s">
         <v>914</v>
       </c>
@@ -42001,7 +42000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A447" s="5" t="s">
         <v>916</v>
       </c>
@@ -42087,7 +42086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A448" s="5" t="s">
         <v>918</v>
       </c>
@@ -42173,7 +42172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A449" s="5" t="s">
         <v>920</v>
       </c>
@@ -42259,7 +42258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A450" s="5" t="s">
         <v>922</v>
       </c>
@@ -42345,7 +42344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A451" s="5" t="s">
         <v>924</v>
       </c>
@@ -42431,7 +42430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A452" s="5" t="s">
         <v>926</v>
       </c>
@@ -42517,7 +42516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A453" s="5" t="s">
         <v>928</v>
       </c>
@@ -42603,7 +42602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A454" s="5" t="s">
         <v>930</v>
       </c>
@@ -42689,7 +42688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A455" s="5" t="s">
         <v>932</v>
       </c>
@@ -42775,7 +42774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A456" s="5" t="s">
         <v>934</v>
       </c>
@@ -42861,7 +42860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:28" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A457" s="5" t="s">
         <v>936</v>
       </c>
@@ -42948,13 +42947,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB457" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="AS12"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AB457" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
